--- a/flipBook Changes.xlsx
+++ b/flipBook Changes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dbs1/Sites/cdn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C562D4-D9AE-AE4B-B892-4D4632075B35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565BF106-5AF5-AA42-8AF5-41D31132BBEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30220" windowHeight="15720" xr2:uid="{F0F24D28-C2FD-A840-A28D-97926ACC1CA6}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="18120" windowHeight="14600" xr2:uid="{F0F24D28-C2FD-A840-A28D-97926ACC1CA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>

--- a/flipBook Changes.xlsx
+++ b/flipBook Changes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dbs1/Sites/cdn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565BF106-5AF5-AA42-8AF5-41D31132BBEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93AB3E3-513E-424E-AFC8-17F617D7A1CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="18120" windowHeight="14600" xr2:uid="{F0F24D28-C2FD-A840-A28D-97926ACC1CA6}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="760" windowWidth="24320" windowHeight="14600" xr2:uid="{F0F24D28-C2FD-A840-A28D-97926ACC1CA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <r>
       <t xml:space="preserve">&lt;link </t>
@@ -66,7 +66,7 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="style/style.css" /&gt;</t>
+      <t>="style/player.css" /&gt;</t>
     </r>
   </si>
   <si>
@@ -109,7 +109,130 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="style/player.css" /&gt;</t>
+      <t>="style/phoneTemplate.css" /&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="javascript/jquery-3.5.1.min.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="javascript/config.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="javascript/LoadingJS.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    &lt;script </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="javascript/main.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="javascript/editor.js"&gt;&lt;/script&gt;</t>
     </r>
   </si>
   <si>
@@ -152,7 +275,7 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="style/phoneTemplate.css" /&gt;</t>
+      <t>="style/template.css" /&gt;</t>
     </r>
   </si>
   <si>
@@ -176,11 +299,51 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="javascript/jquery-3.5.1.min.js"&gt;&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
+      <t>="javascript/MovingBackgrounds.min.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;link </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>rel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="stylesheet" </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>href</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="style/MovingBackgrounds.min.css" /&gt;</t>
+    </r>
   </si>
   <si>
     <r>
@@ -203,7 +366,50 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="javascript/config.js"&gt;&lt;/script&gt;</t>
+      <t>="javascript/FlipBookPlugins.min.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;link </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>rel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="stylesheet" </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>href</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="style/FlipBookPlugins.min.css" /&gt;</t>
     </r>
   </si>
   <si>
@@ -227,31 +433,50 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="javascript/LoadingJS.js"&gt;&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    &lt;script </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>src</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="javascript/main.js"&gt;&lt;/script&gt;</t>
+      <t>="javascript/flipHtml5.hiSlider2.min.js"&gt;&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;link </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>rel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="stylesheet" </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>href</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.3"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="3"/>
+      </rPr>
+      <t>="style/hiSlider2.min.css" /&gt;</t>
     </r>
   </si>
   <si>
@@ -275,274 +500,6 @@
         <rFont val="Menlo"/>
         <family val="3"/>
       </rPr>
-      <t>="javascript/editor.js"&gt;&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;link </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>rel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">="stylesheet" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>href</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="style/template.css" /&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;script </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>src</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="javascript/MovingBackgrounds.min.js"&gt;&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;link </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>rel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">="stylesheet" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>href</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="style/MovingBackgrounds.min.css" /&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;script </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>src</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="javascript/FlipBookPlugins.min.js"&gt;&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;link </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>rel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">="stylesheet" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>href</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="style/FlipBookPlugins.min.css" /&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;script </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>src</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="javascript/flipHtml5.hiSlider2.min.js"&gt;&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;link </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>rel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">="stylesheet" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>href</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="style/hiSlider2.min.css" /&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;script </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>src</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
       <t>="slide_javascript/slideJS.js"&gt;&lt;/script&gt;</t>
     </r>
   </si>
@@ -569,49 +526,6 @@
   </si>
   <si>
     <t>https://cdn.jsdelivr.net/gh/digitalbiblesociety/cdn/flip/</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;link </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>rel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">="stylesheet" </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>href</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.3"/>
-        <color theme="1"/>
-        <rFont val="Menlo"/>
-        <family val="3"/>
-      </rPr>
-      <t>="https://cdn.jsdelivr.net/gh/digitalbiblesociety/cdn/flip/style/style.css" /&gt;</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1448,79 +1362,75 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -1529,10 +1439,10 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -1541,90 +1451,90 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -1637,18 +1547,18 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
